--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2145,6 +2145,2026 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128620766</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90954</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>544875</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7014217</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128620688</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>544904</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7013692</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128620764</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544863</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7014318</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128620759</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544749</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7014414</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128620686</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544934</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7013741</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128620684</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545015</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7013789</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128620765</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544869</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7014317</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128620752</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>544556</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7014586</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128620689</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>544880</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7013640</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128620757</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>544710</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7014454</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128620682</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545134</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7013685</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128620687</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544868</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7013732</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128620685</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>544927</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7013751</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128620683</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>545044</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7013721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128620758</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90954</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>544745</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7014419</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128620761</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92774</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>544854</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128620767</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92758</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>544888</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7014243</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128620681</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>545163</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7013806</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128620768</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>544964</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7014248</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128620750</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>544868</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7013660</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128620759</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>128620687</v>
       </c>
       <c r="B25" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92774</v>
+        <v>92780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92758</v>
+        <v>92764</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92780</v>
+        <v>92786</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92764</v>
+        <v>92770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92786</v>
+        <v>92788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128620759</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>128620687</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92789</v>
+        <v>92816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92821</v>
+        <v>92828</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128620759</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>128620687</v>
       </c>
       <c r="B25" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128620759</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>128620687</v>
       </c>
       <c r="B25" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>92837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 12040-2025 artfynd.xlsx
+++ b/artfynd/A 12040-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>128620766</v>
       </c>
       <c r="B14" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128620688</v>
       </c>
       <c r="B15" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>128620764</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>128620686</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>128620684</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>128620765</v>
       </c>
       <c r="B20" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>128620752</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>128620689</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128620757</v>
       </c>
       <c r="B23" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128620682</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>128620685</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>128620683</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128620758</v>
       </c>
       <c r="B28" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128620761</v>
       </c>
       <c r="B29" t="n">
-        <v>92845</v>
+        <v>92853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>128620767</v>
       </c>
       <c r="B30" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>128620681</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>128620768</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128620750</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
